--- a/output/universities.xlsx
+++ b/output/universities.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="82" customWidth="1" min="4" max="4"/>
     <col width="85" customWidth="1" min="5" max="5"/>
     <col width="105" customWidth="1" min="6" max="6"/>
     <col width="86" customWidth="1" min="7" max="7"/>
@@ -470,34 +470,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Prof. Moses Musinguzi, PhD</t>
+          <t>Agabirwe Patience</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/01/Prof_Muzinguzi.jpg</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Prof._Moses_Musinguzi,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -507,34 +503,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Kizito Maria Kasule, PhD</t>
+          <t>Agnes Nakakawa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Head of Department – IS /... Read More</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Assoc.-Prof.-Kizito-Maria-Kasule-292x300.jpg</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Kizito_Maria_Kasule,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,34 +536,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Prof. Henry Mwanaki Alinaitwe, PhD</t>
+          <t>Agnes Rwashana Semwanga</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assoc. Professor.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/Prof.-Eng.-Henry-Mwanaki-.jpg</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Prof._Henry_Mwanaki_Alinaitwe,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -581,34 +569,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Prof. Umaru Bagampadde, PhD</t>
+          <t>Alex Mwotil</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/05/AssocProfUmaruBagampadde-300x300.jpeg</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Prof._Umaru_Bagampadde,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -618,34 +602,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Prof. John Baptist Kirabira</t>
+          <t>Alice Nandawula Mugisha</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Baptist-260x300.png</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Prof._John_Baptist_Kirabira.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -655,34 +635,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Anthony Gidudu, PhD</t>
+          <t>Amanda Irene Birungi</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/anthony.png</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Anthony_Gidudu,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -692,34 +668,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Amanda Tumusiime, PhD</t>
+          <t>Annabella Basaza-Ejiri</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/Amanda.png</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Amanda_Tumusiime,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -729,34 +701,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Eng. Dr. Dorothy Okello</t>
+          <t>Arinaitwe Irene</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/08/Dorothy-Okello-Dean-300x284.png</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Eng._Dr._Dorothy_Okello.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -766,34 +734,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Kakande Angelo</t>
+          <t>Asiimwe Paddy Junior</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Prof-Angelo-285x300.jpg</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Kakande_Angelo.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -803,34 +767,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Assoc. Prof.  Peter Wilberforce Olupot, PhD</t>
+          <t>Asio Evelyn Patra K</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/05/Dr-Peter-Olupot-254x300.jpg</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof.__Peter_Wilberforce_Olupot,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -840,34 +800,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Charles Niwagaba Buregeya, PhD</t>
+          <t>Barbara Nansamba</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/AssocProfCharlesNiwagaba-300x300.jpeg</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Charles_Niwagaba_Buregeya,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -877,34 +833,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Michael Lubwama, PhD</t>
+          <t>Batte Richard</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/dr-lubwama-288x300.png</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Michael_Lubwama,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -914,34 +866,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Stephen Mukiibi</t>
+          <t>Benard Muwonge Sajjabbi</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/Assoc_Mukiibi.png</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Stephen_Mukiibi.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -951,34 +899,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dr. Nathan Kibwami, PhD</t>
+          <t>Benjamin Kanagwa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/Dr.-Nathan-Kibwami2-254x300-1.jpg</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Nathan_Kibwami,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -988,34 +932,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dr. Musenze Ronald, PhD</t>
+          <t>Bitwire George Albert</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/06/16-254x300-1.jpg</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Musenze_Ronald,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1025,22 +965,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dr. Emmanuel Wokulira Miyingo, PhD</t>
+          <t>Bukirwa Joyce Muwanguzi</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1058,34 +998,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jane Namaganda-Kiyimba</t>
+          <t>Chongomweru Halimu</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Jane_Namaganda-Kiyimba-277x300.jpg</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Jane_Namaganda-Kiyimba.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1095,34 +1031,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Lydia Kayondo Ndandiko Mazzi, PhD</t>
+          <t>Daudi Jjingo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/lydia.png</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Lydia_Kayondo_Ndandiko_Mazzi,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1132,34 +1064,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dr. Amin Tamale Kiggundu, PhD</t>
+          <t>Drake Patrick Mirembe</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer... Read More</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/12/kiggundu.jpg</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Amin_Tamale_Kiggundu,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1169,34 +1097,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Nakawunde Robinah Kulabako, PhD</t>
+          <t>Ekwaro Francis</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/05/DrRobinahKulabako.jpg</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Assoc._Prof._Nakawunde_Robinah_Kulabako,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1206,34 +1130,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dr. Betty Nabubuma, PhD</t>
+          <t>Emily Bagarukayo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Senior Lecturer Department: Information... Read More</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Nabuma.png</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Betty_Nabubuma,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,34 +1163,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dr. Kimuli Ismail, PhD</t>
+          <t>Emmanuel Lule</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/WhatsApp-Image-2026-02-09-at-10.19.28-1-300x300.jpeg</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Kimuli_Ismail,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1280,34 +1196,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dr. Tumusiime Edmund, PhD</t>
+          <t>Emmanuel Mugejjera</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Dr-Tumusiime-Edmund-300x300.jpeg</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Tumusiime_Edmund,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1317,34 +1229,30 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Joseph Jjagwe</t>
+          <t>Engineer Bainomugisha</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Head of Department – Computer Science... Read More</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Jaggwe.jpeg</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Joseph_Jjagwe.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1354,34 +1262,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Medard Turyasingura</t>
+          <t>Evelyn Kigozi Kahiigi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/medard.jpeg</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Medard_Turyasingura.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1391,34 +1295,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dr. Fildah Ayaa, PhD</t>
+          <t>Fiona Ssozi</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Dr.-Fildah-Ayaa.jpeg</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Fildah_Ayaa,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1428,34 +1328,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Dr Moses Matovu, PhD</t>
+          <t>Flavia Namagembe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/06/DrMosesMatovu.jpeg</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr_Moses_Matovu,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1465,34 +1361,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dr. Sempewo Jotham Ivan, PhD</t>
+          <t>Florence Nameere Kivunike</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Dr.-Sempewo-Jotham-Ivan.jpeg</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Sempewo_Jotham_Ivan,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1502,34 +1394,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dr. Abubaker Matovu Waswa, PhD</t>
+          <t>Golooba Moses</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Dr.-Abubaker-Matovu-Waswa-262x300.png</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Abubaker_Matovu_Waswa,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1539,34 +1427,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Dr. Edwin Mugume, PhD</t>
+          <t>Grace Bugembe Kamulegeya</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer Department:... Read More</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/DrEdwinMugume.jpeg</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Edwin_Mugume,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1576,34 +1460,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Dr. Jonathan Serugunda, PhD</t>
+          <t>Grace Kobusinge</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer Department: Information Systems... Read More</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/DrJonathanSerugunda.jpeg</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Jonathan_Serugunda,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1613,34 +1493,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Dr. Geoffrey Bakkabulindi, PhD</t>
+          <t>Hawa Nyende</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/DrGeoffreyBakkabulindi-300x300.jpeg</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Geoffrey_Bakkabulindi,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1650,34 +1526,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Dr. Andrew Katumba, PhD</t>
+          <t>Innocent Ndibatya</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/andrew-katumba-300x300.png</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Andrew_Katumba,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1687,22 +1559,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Dr. Mukasa Nobert, PhD</t>
+          <t>Joab Ezra Agaba</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer Department: Networks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1720,22 +1592,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Dr. Namutebi May, PhD</t>
+          <t>John Kizito</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer Department: Computer... Read More</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1753,34 +1625,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Dr. Roseline N. Akol, PhD</t>
+          <t>John Ngubiri</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/rose-akol-200x300.jpg</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Dr._Roseline_N._Akol,_PhD.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1790,34 +1658,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Mr. Frank Ssemakula</t>
+          <t>Johnson Mwebaze</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Mr-Frank-Ssemakula-240x300.jpg</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Mr._Frank_Ssemakula.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1827,34 +1691,30 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Agatha Turyagyenda Amara</t>
+          <t>Joseph Kibombo Balikuddembe</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Dean – School of Computing and Information Technology (SCIT),... Read More</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/MsAgathaTuryagenda-300x300.jpeg</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>output\images\Makerere_University_Agatha_Turyagyenda_Amara.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1864,22 +1724,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Dr. Dativa Tizikara, PhD</t>
+          <t>Josephine Nabukenya</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assoc. Professor</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1897,22 +1757,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Dr. Cosmas Mwikirize, PhD</t>
+          <t>Joyce Nabende Nakatumba</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Senior Lecturer Department:... Read More</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1930,22 +1790,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Dr. Nyenje Mayanja Philip, PhD</t>
+          <t>Julianne Sansa Otim</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1963,22 +1823,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Dr. Gilbert Joseph Kasangaki</t>
+          <t>Kacunguzi Twinoburyo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1996,22 +1856,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Murungi Philip</t>
+          <t>Kaddu Sarah Birungi</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Dean – East Africa School of Library and Information Science... Read More</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2029,22 +1889,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>David Kaddu</t>
+          <t>Katende Jacob</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2062,22 +1922,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Alinaitwe Lynda Mutesi</t>
+          <t>Kiconco Christine</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2095,22 +1955,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Dr. Nabuyungo Ritah Edopu, PhD</t>
+          <t>Komugisha Lilian</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2128,22 +1988,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kato Abbey</t>
+          <t>Kulisooma Ezerea</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2161,22 +2021,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Dr. Fidelis Nabukenya Matovu, PhD</t>
+          <t>Kutyamukama Alice Gitta</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2194,22 +2054,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Dr. Karungi Doreen, PhD</t>
+          <t>Luyombya David</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Head of Department / Assoc. Professor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2227,22 +2087,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Dr. Mwesigwa Stephen, PhD</t>
+          <t>Magara Elisam</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2260,22 +2120,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Kanuge J.B, PhD</t>
+          <t>Male Vincent</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2293,22 +2153,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Dr. Kasozi Dorah Namutebi, PhD</t>
+          <t>Marriette Atuhuriire Katarahweire</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer / HoD – Computer... Read More</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2326,22 +2186,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Dr. Mpindi Kibude Ronald, PhD</t>
+          <t>Marvin Ggaliwango</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2359,22 +2219,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Dr. Kabiito Richard, PhD</t>
+          <t>Mary Nsabagwa</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer Department: Networks</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2392,22 +2252,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Nsereko Joseph Raymond</t>
+          <t>Mercy Rebekah Amiyo</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2425,22 +2285,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Dr. Namakula Hidaya, PhD</t>
+          <t>Michael Kizito</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PhD</t>
+          <t>Lecturer Department: Computer Science... Read More</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2458,22 +2318,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Kaweesi Ronald</t>
+          <t>Moses Ntanda Kyebambe</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2491,22 +2351,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kyeeru Hilda</t>
+          <t>Mutibwa Lois Nankya</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Assistant Lecturer Department:... Read More</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2524,22 +2384,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Godwin Obali</t>
+          <t>Muzaki Faridah</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2557,22 +2417,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Naome Bagyenda Kayonda</t>
+          <t>Mwanje Ssenono Aloysius</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Assistant Lecturer Department:... Read More</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2590,22 +2450,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Menu links</t>
+          <t>Nagwovuma Margaret</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2623,22 +2483,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Useful links</t>
+          <t>Nalumansi Mary</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer / HoD. Library... Read More</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2656,22 +2516,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>College of Engineering, Design, Art &amp; Technology</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CEDAT</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Resources</t>
+          <t>Namatovu Hasifah Kasujja</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2684,286 +2544,258 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gulu University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Faculty not Specified</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Dr. Apio Esther</t>
+          <t>Namirembe Esther</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dr. Apio Esther (MMED, MBChB, Dip Physiotherapy) is an Associate Consultant Phys...</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://gu.ac.ug/wp-content/uploads/2026/06/Screenshot-2026-06-18-102246.png</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>output\images\Gulu_University_Dr._Apio_Esther.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Gulu University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Faculty not Specified</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ojara Williams Francis</t>
+          <t>Namujuzi Sylvia</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ojara Williams Francis, PhD is a Ugandan pharmacologist and academic dedicated t...</t>
+          <t>Lecturer / HoD. Records and Archives... Read More</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://gu.ac.ug/wp-content/uploads/2026/06/Ojara-Williams-Francis.png</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>output\images\Gulu_University_Ojara_Williams_Francis.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gulu University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Faculty not Specified</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Otto Ben Adol</t>
+          <t>Nasser Kimbugwe</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dr. Otto Ben Adol is a seasoned development practitioner and academic with over ...</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://gu.ac.ug/wp-content/uploads/2026/06/Dr.-Otto-Ben-Adol--e1781174704502.jpg</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>output\images\Gulu_University_Otto_Ben_Adol.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gulu University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Faculty not Specified</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Dr. Fredrick Bongomin Okello</t>
+          <t>Odongo Steven Eyobu</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dr. Fredrick Bongomin Okello (MBChB, MMed Internal Medicine) is an Associate Con...</t>
+          <t>Lecturer Department:... Read More</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://gu.ac.ug/wp-content/uploads/2026/05/Fredrick-Bongomin--e1779963152604-351x348.png</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>output\images\Gulu_University_Dr._Fredrick_Bongomin_Okello.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gulu University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Faculty not Specified</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Academic Staff</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kenneth Kidega</t>
+          <t>Okello-Obura Constant</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mr. Kenneth Kidega is currently pursuing a PhD in Agriculture and Applied Biosci...</t>
+          <t>Professor</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://gu.ac.ug/wp-content/uploads/2026/05/Kenneth-Kidega-e1779785842513.jpg</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>output\images\Gulu_University_Kenneth_Kidega.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Prof. J. M. Kaura</t>
+          <t>Peter Nabende</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Deputy Principal / Senior Lecturer</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/dean/eng.jpeg</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Prof._J._M._Kaura.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Dr. A. A. Murana</t>
+          <t>Peter Wakholi</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Deputy Dean</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/staff/Murana.png</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Dr._A._A._Murana.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mr.</t>
+          <t>Rashidah Kasauli Namisanvu</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Faculty Officer</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2976,261 +2808,3364 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Mal. Ibrahim Mohammed</t>
+          <t>Raymond Mugwanya</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Assistant Faculty Officer</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/staff/ibrahimmohammed.jpg</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Mal._Ibrahim_Mohammed.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Mr. Nache M. Anthony</t>
+          <t>Rehema Baguma</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Group Accountant</t>
+          <t>Assoc. Professor</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/staff/Nache.jpg</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Mr._Nache_M._Anthony.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mal. Ado Usman</t>
+          <t>Rose Nakasi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Maintanace Officer</t>
+          <t>Lecturer Department: Information Technology... Read More</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/staff/ado.jpg</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Mal._Ado_Usman.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Mr. James O. Ameje</t>
+          <t>Rose Nakibuule</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dean's Personal Assistant</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/staff/jamesameje.jpg</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Mr._James_O._Ameje.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mrs. Suzannah P. Bulus</t>
+          <t>Ruth Mbabazi Mutebi</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Secretary</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/staff/pofisuzannah.jpg</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Mrs._Suzannah_P._Bulus.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mal. Aliyu Balarabe</t>
+          <t>Serugunda Henry Mukalazi</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>House Keeper</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/staff/aliyubalarabe.jpg</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Mal._Aliyu_Balarabe.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ahmadu Bello University</t>
+          <t>Makerere University</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Faculty of Engineering</t>
+          <t>College of Computing &amp; Information Sciences</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>not Specified</t>
+          <t>CoCIS</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mr. James Mikah</t>
+          <t>Ssekitto Francis</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>House Keeper</t>
+          <t>Assistant Lecturer</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://engineering.abu.edu.ng/assets/images/staff/jamesmikah.jpg</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>output\images\Ahmadu_Bello_University_Mr._James_Mikah.jpg</t>
-        </is>
-      </c>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>College of Computing &amp; Information Sciences</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CoCIS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Swaib Dragule</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer Department: Computer... Read More</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>College of Computing &amp; Information Sciences</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CoCIS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Swaib Kyanda Kaawaase</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Head of Department – Networks / Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>College of Computing &amp; Information Sciences</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CoCIS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Tonny Eddie Bulega</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Lecturer Department: Networks... Read More</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>College of Computing &amp; Information Sciences</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CoCIS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Tulinayo P. Fiona</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Head of Department – IT... Read More</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Prof. Moses Musinguzi, PhD</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/01/Prof_Muzinguzi.jpg</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Prof._Moses_Musinguzi,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Kizito Maria Kasule, PhD</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Assoc.-Prof.-Kizito-Maria-Kasule-292x300.jpg</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Kizito_Maria_Kasule,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Prof. Henry Mwanaki Alinaitwe, PhD</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/Prof.-Eng.-Henry-Mwanaki-.jpg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Prof._Henry_Mwanaki_Alinaitwe,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Prof. Umaru Bagampadde, PhD</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/05/AssocProfUmaruBagampadde-300x300.jpeg</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Prof._Umaru_Bagampadde,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Prof. John Baptist Kirabira</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Baptist-260x300.png</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Prof._John_Baptist_Kirabira.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Anthony Gidudu, PhD</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/anthony.png</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Anthony_Gidudu,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Amanda Tumusiime, PhD</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/Amanda.png</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Amanda_Tumusiime,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Eng. Dr. Dorothy Okello</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/08/Dorothy-Okello-Dean-300x284.png</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Eng._Dr._Dorothy_Okello.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Kakande Angelo</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Prof-Angelo-285x300.jpg</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Kakande_Angelo.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Assoc. Prof.  Peter Wilberforce Olupot, PhD</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/05/Dr-Peter-Olupot-254x300.jpg</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof.__Peter_Wilberforce_Olupot,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Charles Niwagaba Buregeya, PhD</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/AssocProfCharlesNiwagaba-300x300.jpeg</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Charles_Niwagaba_Buregeya,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Michael Lubwama, PhD</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/dr-lubwama-288x300.png</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Michael_Lubwama,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Stephen Mukiibi</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/Assoc_Mukiibi.png</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Stephen_Mukiibi.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Dr. Nathan Kibwami, PhD</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/Dr.-Nathan-Kibwami2-254x300-1.jpg</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Nathan_Kibwami,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Dr. Musenze Ronald, PhD</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/06/16-254x300-1.jpg</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Musenze_Ronald,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Dr. Emmanuel Wokulira Miyingo, PhD</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jane Namaganda-Kiyimba</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Jane_Namaganda-Kiyimba-277x300.jpg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Jane_Namaganda-Kiyimba.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Lydia Kayondo Ndandiko Mazzi, PhD</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/02/lydia.png</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Lydia_Kayondo_Ndandiko_Mazzi,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Dr. Amin Tamale Kiggundu, PhD</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/12/kiggundu.jpg</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Amin_Tamale_Kiggundu,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Assoc. Prof. Nakawunde Robinah Kulabako, PhD</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/05/DrRobinahKulabako.jpg</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Assoc._Prof._Nakawunde_Robinah_Kulabako,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Dr. Betty Nabubuma, PhD</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/03/Nabuma.png</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Betty_Nabubuma,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Dr. Kimuli Ismail, PhD</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/WhatsApp-Image-2026-02-09-at-10.19.28-1-300x300.jpeg</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Kimuli_Ismail,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Dr. Tumusiime Edmund, PhD</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Dr-Tumusiime-Edmund-300x300.jpeg</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Tumusiime_Edmund,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Joseph Jjagwe</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Jaggwe.jpeg</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Joseph_Jjagwe.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Medard Turyasingura</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/medard.jpeg</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Medard_Turyasingura.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Dr. Fildah Ayaa, PhD</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Dr.-Fildah-Ayaa.jpeg</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Fildah_Ayaa,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Dr Moses Matovu, PhD</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2025/06/DrMosesMatovu.jpeg</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr_Moses_Matovu,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Dr. Sempewo Jotham Ivan, PhD</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Dr.-Sempewo-Jotham-Ivan.jpeg</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Sempewo_Jotham_Ivan,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Dr. Abubaker Matovu Waswa, PhD</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Dr.-Abubaker-Matovu-Waswa-262x300.png</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Abubaker_Matovu_Waswa,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Dr. Edwin Mugume, PhD</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/DrEdwinMugume.jpeg</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Edwin_Mugume,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Dr. Jonathan Serugunda, PhD</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/DrJonathanSerugunda.jpeg</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Jonathan_Serugunda,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Dr. Geoffrey Bakkabulindi, PhD</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/DrGeoffreyBakkabulindi-300x300.jpeg</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Geoffrey_Bakkabulindi,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Dr. Andrew Katumba, PhD</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/andrew-katumba-300x300.png</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Andrew_Katumba,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Dr. Mukasa Nobert, PhD</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Dr. Namutebi May, PhD</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Dr. Roseline N. Akol, PhD</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/rose-akol-200x300.jpg</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Dr._Roseline_N._Akol,_PhD.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Mr. Frank Ssemakula</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/Mr-Frank-Ssemakula-240x300.jpg</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Mr._Frank_Ssemakula.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Agatha Turyagyenda Amara</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://cedat.mak.ac.ug/wp-content/uploads/2026/02/MsAgathaTuryagenda-300x300.jpeg</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>output\images\Makerere_University_Agatha_Turyagyenda_Amara.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Dr. Dativa Tizikara, PhD</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Dr. Cosmas Mwikirize, PhD</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Dr. Nyenje Mayanja Philip, PhD</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Dr. Gilbert Joseph Kasangaki</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Murungi Philip</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>David Kaddu</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Alinaitwe Lynda Mutesi</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Dr. Nabuyungo Ritah Edopu, PhD</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Kato Abbey</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Dr. Fidelis Nabukenya Matovu, PhD</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Dr. Karungi Doreen, PhD</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Dr. Mwesigwa Stephen, PhD</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Kanuge J.B, PhD</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Dr. Kasozi Dorah Namutebi, PhD</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Dr. Mpindi Kibude Ronald, PhD</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Dr. Kabiito Richard, PhD</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Nsereko Joseph Raymond</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Dr. Namakula Hidaya, PhD</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>PhD</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Kaweesi Ronald</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Kyeeru Hilda</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Godwin Obali</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Naome Bagyenda Kayonda</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Menu links</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Useful links</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Makerere University</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>College of Engineering, Design, Art &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CEDAT</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Gulu University</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Faculty not Specified</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Dr. Apio Esther</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Dr. Apio Esther (MMED, MBChB, Dip Physiotherapy) is an Associate Consultant Phys...</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://gu.ac.ug/wp-content/uploads/2026/06/Screenshot-2026-06-18-102246.png</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>output\images\Gulu_University_Dr._Apio_Esther.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Gulu University</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Faculty not Specified</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Ojara Williams Francis</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Ojara Williams Francis, PhD is a Ugandan pharmacologist and academic dedicated t...</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://gu.ac.ug/wp-content/uploads/2026/06/Ojara-Williams-Francis.png</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>output\images\Gulu_University_Ojara_Williams_Francis.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Gulu University</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Faculty not Specified</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Otto Ben Adol</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Dr. Otto Ben Adol is a seasoned development practitioner and academic with over ...</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://gu.ac.ug/wp-content/uploads/2026/06/Dr.-Otto-Ben-Adol--e1781174704502.jpg</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>output\images\Gulu_University_Otto_Ben_Adol.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Gulu University</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Faculty not Specified</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Dr. Fredrick Bongomin Okello</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Dr. Fredrick Bongomin Okello (MBChB, MMed Internal Medicine) is an Associate Con...</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://gu.ac.ug/wp-content/uploads/2026/05/Fredrick-Bongomin--e1779963152604-351x348.png</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>output\images\Gulu_University_Dr._Fredrick_Bongomin_Okello.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Gulu University</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Faculty not Specified</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Kenneth Kidega</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Mr. Kenneth Kidega is currently pursuing a PhD in Agriculture and Applied Biosci...</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://gu.ac.ug/wp-content/uploads/2026/05/Kenneth-Kidega-e1779785842513.jpg</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>output\images\Gulu_University_Kenneth_Kidega.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Academic Calendar</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Alumni Affairs</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Council</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Quick Links</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>UPU E-system</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Get In Touch</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Academic Calendar</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Alumni Affairs</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Council</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Ankole Western University</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>1st Graduation List for the 7th Graduation Ceremony of AWU 2024</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Tuhairwe shiberah</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Ankole Western University</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>1st Graduation List for the 7th Graduation Ceremony of AWU 2024</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Katungwensi Derick</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/universities.xlsx
+++ b/output/universities.xlsx
@@ -413,12 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="82" customWidth="1" min="4" max="4"/>
     <col width="85" customWidth="1" min="5" max="5"/>
     <col width="105" customWidth="1" min="6" max="6"/>
@@ -5575,28 +5575,32 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr"/>
+          <t>Dr. Kirya Fred</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Associate Professor/Dean SHS/ Senate Rep. To Council</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G152" t="inlineStr"/>
@@ -5604,28 +5608,32 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr"/>
+          <t>Dr. Othieno Emmanuel</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -5633,28 +5641,32 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>Dr. Ntale Roman Saba</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G154" t="inlineStr"/>
@@ -5662,28 +5674,32 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr"/>
+          <t>Dr. Aderu David</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G155" t="inlineStr"/>
@@ -5691,27 +5707,27 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Academic Calendar</t>
+          <t>Dr. Katongole Paul</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5724,27 +5740,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Alumni Affairs</t>
+          <t>Dr. Winifred Nabwire Wafula</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5757,27 +5773,27 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Council</t>
+          <t>Dr. Eleku Simon</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5790,27 +5806,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Uganda Pentecostal University</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Quick Links</t>
+          <t>Dr. Richard Mpango</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5823,27 +5839,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Uganda Pentecostal University</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>UPU E-system</t>
+          <t>Dr. Kabwigu Samuel</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5856,27 +5872,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Uganda Pentecostal University</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Get In Touch</t>
+          <t>Dr. Amuron Naomi</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5889,28 +5905,32 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr"/>
+          <t>Dr. Luwede Aliba Flavia</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -5918,28 +5938,32 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
+          <t>Dr. Olupot Robert</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -5947,28 +5971,32 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
+          <t>Mr. Mwesige Samuel</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G164" t="inlineStr"/>
@@ -5976,28 +6004,32 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
+          <t>Mr. Munguiko Clement</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -6005,27 +6037,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Academic Calendar</t>
+          <t>Mr. Kateregga James</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6038,27 +6070,27 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Alumni Affairs</t>
+          <t>Mr. Otim Paul</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6071,27 +6103,27 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Council</t>
+          <t>Ms. Nabusige Jean Brenda Gesa</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6104,27 +6136,27 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ankole Western University</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Soroti University</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>1st Graduation List for the 7th Graduation Ceremony of AWU 2024</t>
+          <t>Mr. Emmanuel Denis Morgan Thomas</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Tuhairwe shiberah</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6137,35 +6169,2544 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Dr. Namwase Hadijja Katabira</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Dr. Abwola Mary Olwedo</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Mr. Ojakol Alex Imalingat</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Ms. Kiconco Ritah</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Dr. Bahati Johnson</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Dr. Kirya Musa</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Dr. Opito Ronald</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Dr. Engoru Ejoru Charles</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Mr. Kizito Mark</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Mr. Yahaya Joseph James</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Ms. Atim Letizia</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Ms. Namujju Josephine</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Mr. Atukwatse Joseph</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Ms. Nankinga Clare</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Dr. Okuja Maxwell</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Mr. Aneth Ephrem Gregory</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Mr. Okello Samuel</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Mr. Okoboi Joash</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Dr. Lwere Kamada</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Mr. Kiguli James Mukasa</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Mr. Adakun Moses</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Dr. Odongo Charles Newton</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Mr. Kizito Mary Muwonge</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Mr. Kinobe Robert</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Ms. Nakalembe Loyce</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Mr. Ayikobua Emmanuel Tiyo</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer/ Academic Staff Rep To Council</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Dr. Cherop Moses</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Ms. Akurut Hellen</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Dr. Lubogo Patrick</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Dr. Kyegombe William</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Dr. Apolot Denis</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Mr. Nkangi Lwanga Eriasaph</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Chief Technician</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Ms. Apolot Esther</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Lab Attendant</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Ms. Cheptoek Sarah Musani</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Lab Technician</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Mr. Aculet Valentine</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Laboratory Technician</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Ms. Akello Safina</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Skills Lab Instructor</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Mr. Apedel Micheal</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Lab Attendant</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Mr. Baguma Kenneth</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Lab Technician</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Mr. Etanu Simon</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Lab Attendant</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Mr. Malinga Gerald Patrick</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Lab Assistant</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Mr. Musilimu Pamba</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Laboratory Technician</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Ms. Nabwire Sandra</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Science Laboratory Assistant</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Mr. Nuwamanya Newton</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Laboratory Technician</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Mr. Ocan Samuel</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Laboratory Technician</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Mr. Ojuko Samuel</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Laboratory Technician</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Mr. Ojula Emmanuel</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Lab Attendant</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Mr. Opiding Francis</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Laboratory Technician</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Mr. Opio James Peter</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Lab Attendant</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Mr. Otim Jimmy Shadrack</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Lab Assistant</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Mr. Ruhangariyo Robert</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Lab Technician</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Ms. Awino Mariam Abdallah</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Assistant Administrator</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Mr. Sengendo Geofrey</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Mr. Ahimbisibwe Octavious</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Ms. Mone Tina</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Senior Administrator</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Mr. Epou Solomon</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Office Assistant</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Mr. Osuwat Lawrence Obado</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Student Services</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Academics</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Useful Links</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Academic Calendar</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Alumni Affairs</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Council</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Quick Links</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>UPU E-system</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Get In Touch</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Academic Calendar</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Alumni Affairs</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Council</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
           <t>Ankole Western University</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B246" t="inlineStr">
         <is>
           <t>Auto-detected</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C246" t="inlineStr">
         <is>
           <t>Auto-detected</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>1st Graduation List for the 7th Graduation Ceremony of AWU 2024</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Tuhairwe shiberah</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Ankole Western University</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>1st Graduation List for the 7th Graduation Ceremony of AWU 2024</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
         <is>
           <t>Katungwensi Derick</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Image not Found</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/universities.xlsx
+++ b/output/universities.xlsx
@@ -413,12 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G247"/>
+  <dimension ref="A1:G416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="82" customWidth="1" min="4" max="4"/>
     <col width="85" customWidth="1" min="5" max="5"/>
     <col width="105" customWidth="1" min="6" max="6"/>
@@ -8116,28 +8116,32 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr"/>
+          <t>Prof. Dr. Jasper Ogwal Okeng</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Vice Chancellor</t>
+        </is>
+      </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G229" t="inlineStr"/>
@@ -8145,28 +8149,32 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr"/>
+          <t>Assoc.  Prof. Okaka Opio Dokotum</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Deputy VC - Academics</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G230" t="inlineStr"/>
@@ -8174,28 +8182,32 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr"/>
+          <t>CPA. Nathan Hasahya Hagobi</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Deputy VC - Finance</t>
+        </is>
+      </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G231" t="inlineStr"/>
@@ -8203,28 +8215,32 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr"/>
+          <t>Mr. Augustine Oyang Atubo</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>University Secretary</t>
+        </is>
+      </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G232" t="inlineStr"/>
@@ -8232,27 +8248,27 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Academic Calendar</t>
+          <t>Mr. Andrew Ojulong</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>University Librarian</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -8265,27 +8281,27 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Alumni Affairs</t>
+          <t>Mr. Angela Geoffrey</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Academic Registrar</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -8298,27 +8314,27 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Islamic University In Uganda</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Council</t>
+          <t>Mrs. Emma Aceng Okite</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Dean of Students</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -8331,27 +8347,27 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Uganda Pentecostal University</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Quick Links</t>
+          <t>Assc. Prof. Dr. Benard Omech</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Director - Graduate Studies &amp; Research</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -8364,27 +8380,27 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Uganda Pentecostal University</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>UPU E-system</t>
+          <t>PROF. Dr. OKELLO TOM RICHARD</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -8397,27 +8413,27 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Uganda Pentecostal University</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Get In Touch</t>
+          <t>Dr. Ocen Laury Lawrence</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -8430,28 +8446,32 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
-        </is>
-      </c>
-      <c r="E239" t="inlineStr"/>
+          <t>Dr. Maxson Kenneth Anyolitho</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Senior Lecturer &amp; Deputy Dean FOPH</t>
+        </is>
+      </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G239" t="inlineStr"/>
@@ -8459,28 +8479,32 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
-        </is>
-      </c>
-      <c r="E240" t="inlineStr"/>
+          <t>JOSEPH OLOBO</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G240" t="inlineStr"/>
@@ -8488,28 +8512,32 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr"/>
+          <t>JUDITH AKELLO ABAl</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G241" t="inlineStr"/>
@@ -8517,28 +8545,32 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr"/>
+          <t>AWICHI RICHARD OPAKA</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+          <t>Image not Found</t>
         </is>
       </c>
       <c r="G242" t="inlineStr"/>
@@ -8546,27 +8578,27 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Academic Calendar</t>
+          <t>EDWARD OJUKA</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -8579,27 +8611,27 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Alumni Affairs</t>
+          <t>Dr. OTIM TOM CHARLES</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -8612,27 +8644,27 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Iuiu Mbale</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Council</t>
+          <t>DR.AWIO JOHN PETER</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Senior Lecturer, Medicine Surgery</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -8645,27 +8677,27 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Ankole Western University</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Lira University</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Auto-detected</t>
+          <t>Staff Directory</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>1st Graduation List for the 7th Graduation Ceremony of AWU 2024</t>
+          <t>DR.EPILA JACKIE</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Tuhairwe shiberah</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -8678,35 +8710,5580 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>DR.ALUNYU ANDREW EGWAR</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DR.JIMMY FRANCIS OBONYO</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>DR.ALOL EMMANUEL</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DR.OGWENG PETER</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DR.PETER OPIO OCHENG</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>DR.ETENGU RICHARD</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>DR.LINDA ISMENE APON</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>DR.OLUM FRANCIS</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Senior Lecturer &amp; Dean FOM</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>DR.MARC SAM OPOLLO</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Senior Lecturer &amp; Dean FoPH</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DR.ELIZABETH AMONGI (P.H.D)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>MR. OGULE Jacob</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>MR. OGULE Jacob</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Assoc. Professor Edward Kumakech</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Professor</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Dr. Samson Udho</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>DR.KWENYA KENETH</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>TEACHING ASSISTANT</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>DR.OKELLO IVAN ODONGO</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DR.RUGUT CORNELIVS KIPLETING</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>DR.JOHN KINTU</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>DR. NAKAZIBA REBECCA</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>DR.ANNA AGNES ARACH</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Nelson Ojuka</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Senior Lecturer AND Dean FOC</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>AUMA ANNA GRACE</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Senior Lecturer AND Dean FNM</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>EBOYU FRANCIS</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Senior Lecturer Psychiatry</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>OKELLO ALEX</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>CHRISTINE JOY ABEJA</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>AKECH STELLA IMMACULATE</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>AKELLO ANNE RUTH</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Mr. Usama Kasekende</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Principal IT Officer</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>BARNABAS TWESIGE</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Dupty Academic Registrar</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>KILAMA WILFRED ACAYO</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Dupty Academic Registrar</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Akite Miriam</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Lecturer &amp; Deputy Dean FOC</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>OPIO PATRICK</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Senior Communications Officer</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>OPIO MOSES</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Assistant Academic Registrar</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>OBONG GERALD JAMES</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Assistant Academic Registrar</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>OREE MOLLY GRACE</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Senior Assistant Registrar</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>BUNGA SAMUEL</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Assistant Academic Registrar</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>KWIZERA GAD</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>FREDA AMITO OCENG</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Lecturer &amp; HOD Nutrition</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>FELISTER APILI</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Lecturer &amp; HOD Midwifery</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>AUMA PAMELLA</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>AWOR FLORENCE</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>NSISI CHRISTINE</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>OBOTE DENNIS</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>VICKY CAROLINE ACHAYO</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>AYO EUNICE</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>WANYONYI MASINDE GEOFFERY</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>ERIC MURUNGI BALUKU</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>BRENDA NINSIIMA</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>NAMUKWANA BETH</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>TOM OMUTE</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>OPIO MAXWELL</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>OGWANG JOHN</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NABASIRYE OAROLINE KAMBUGU</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>DR.ONYANGA NIXON</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>OKELLO SAMUEL</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>OKORI HILDER</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>ENYANG JOLLY JOE.B</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ATUHAIRE EVAS</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>MADIRA EMMANUEL</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>OPIO BOSCO</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>OMIA GEOFFERY</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>MUSOSA MUZATHAM</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Lecturer &amp; HOD - Economics</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>OKILA NIXON</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>OGAL DENIS</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Mr. Musinguzi Marvin</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>APIO SHARON</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>APIO SARA OKITE</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>OKELLO GEOFERY</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>REBECCA AWAYO</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>ATIM MIRRIAM ABUCH</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>GONG NELSON</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>AKAO HARRIET</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>OKWEL ARIA JAMES</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>AYO HARRIET</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>ADOKO DENINIS WALTER</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>OMARA RICHARD</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>OGWAL AWIO KENNETH</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer &amp; HOD IT</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>TODO MOSES</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>OPIO ISMAIL</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>OPIO ISMAIL</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>OJOK-OPIO INNOCENT</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>OJOK TONNY</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>OMARA PATRICK</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer &amp; HOD - Computer Science</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>OJOK SIMON</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>ACEN KELLIS PRISCA</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>OGWAL JIMMY ODONGO</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>ACUP WALTER</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>OKELLO INNOCENT LAMBERT</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>OYUGI ALFRED</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>DR.KASULE MUSA</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>DR.MUZUNGU JOHNBAPTIST</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>DR.MUNAABA SHAMINAH</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>CHEPKWURUI JOYCE</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>BUKULU RAPHAEL</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>AMUMPAIRE PETERSON</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>ALOKA BONNY</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>OKWERA DENNISH</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>APILI BRENDA</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>NYIRABYIRINGIRO SHARON</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>WANJIKO DIANA GRACE</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>ANYANGO LUCY</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>OPII JACOB DIDAN</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>OBUA RICHARD</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>ALONYO SHARON</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Dr.OWINY MOSES</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>OBENY ABEL</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>JOEL NABESHYA</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>EKING EMMANUEL</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NAMUTEBI DEBORAH ANDRINAR</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>ASABA MARION</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>NAKIGANGA STELLA</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>AUMA MORINE</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>ACHOLA REBECCA MERCY</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>OKEC PATRICK</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>KIMBOWA PETER</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>ICEL SOLOMON</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Teaching Assistant</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Okullo Martin</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Assistant Admin</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Ojok Flavia</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>About LU</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Academics Unit</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Lira University</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Staff Directory</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Quick Links</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Mr. Philiam Adoma</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Assistant Librarian I</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Mr. Bosco Apparatus Buruga</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Librarian</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Mr. Moses Odeke Osamai</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Assistant Librarian II</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Mr. Moses Samanya</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Assistant Librarian</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Ms. Doreen Eyoru</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Library Assistant I</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Muni University</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Mr. Boniface Agungi</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Library Assistant II</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Assoc.Prof. Tushabe Florence</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Associate Professor</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Dr. Mbuje Joel Webster</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Dr. Senfuka Christopher</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Senior Lecturer</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Dr. Yusuf Nyonyi</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Dr. Aluku Hellen</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Dr. Naryongo Raphael</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Dr. Chemisto Musa Satya</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Ms. Lynn Tar Gutu Janet</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Lecturer/Academic Staff Rep To Council</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Eng. Ivan Tim Oloya</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Lecturer/ Senate Member</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Mr. Hirya Edymond Richard</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Mr. Komaketch Francis Xavier</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Dr. Abubakhari Sserwadda</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Mr. Ssali Hussein</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Mr. Matsiko Joshua</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Assistant Lecturer</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Mr. Ebiju Fabian Dickens</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Industrial Liaison Officer</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Mr. Ejoku Bernard</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Lab Assistant</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Mr. Engwedu William</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Workshop Attendant</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Mr. Odongo Emmanuel</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Mr. Oligo Emmanuel</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Lab Technician</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Mr. Onen Patrick</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Technician</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Mr. Benard Ejoku</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Student Services</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Academics</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Soroti University</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>School of Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>School of Engineering</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Useful Links</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Academic Staff</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Academic Calendar</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Alumni Affairs</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Islamic University In Uganda</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Council</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Quick Links</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>UPU E-system</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Uganda Pentecostal University</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Get In Touch</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>SponsorCentenary BankSupporting the 5th Edition of Run for Girl Child Education.</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/centenary-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Hydration PartnerZora WaterOfficial Hydration Partner for the 5th Edition.</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/zora-water.jpg</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>SponsorSplash KachupaJoining the run for brighter futures and stronger dreams.</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/splash-kachupa.jpg</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Proud SupporterTropical BankHelping keep girls in school through every step.</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>assets/images/home/run4girl-sponsors/tropical-bank.jpg</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Academic Calendar</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Alumni Affairs</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Iuiu Mbale</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Council</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
           <t>Ankole Western University</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>Auto-detected</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C415" t="inlineStr">
         <is>
           <t>Auto-detected</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D415" t="inlineStr">
         <is>
           <t>1st Graduation List for the 7th Graduation Ceremony of AWU 2024</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Tuhairwe shiberah</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Ankole Western University</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Auto-detected</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>1st Graduation List for the 7th Graduation Ceremony of AWU 2024</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
         <is>
           <t>Katungwensi Derick</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>Image not Found</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr"/>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Image not Found</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
